--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_biobio.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_biobio.xlsx
@@ -375,496 +375,496 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Curanilahue</t>
         </is>
       </c>
       <c r="C2">
-        <v>183150</v>
+        <v>93.99677438623738</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Lota</t>
         </is>
       </c>
       <c r="C3">
-        <v>162131</v>
+        <v>93.38779114692571</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Talcahuano</t>
+          <t>Contulmo</t>
         </is>
       </c>
       <c r="C4">
-        <v>120709</v>
+        <v>93.19176527800292</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coronel</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="C5">
-        <v>106575</v>
+        <v>93.1684741313808</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>San Pedro de la Paz</t>
+          <t>Tirúa</t>
         </is>
       </c>
       <c r="C6">
-        <v>96347</v>
+        <v>92.90832945556073</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hualpén</t>
+          <t>Negrete</t>
         </is>
       </c>
       <c r="C7">
-        <v>74627</v>
+        <v>92.76441216522923</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chiguayante</t>
+          <t>Mulchén</t>
         </is>
       </c>
       <c r="C8">
-        <v>67421</v>
+        <v>92.67762123088249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tomé</t>
+          <t>Quilleco</t>
         </is>
       </c>
       <c r="C9">
-        <v>49972</v>
+        <v>92.65607146566947</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Penco</t>
+          <t>Los Alamos</t>
         </is>
       </c>
       <c r="C10">
-        <v>42838</v>
+        <v>92.57080131723382</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lota</t>
+          <t>Cañete</t>
         </is>
       </c>
       <c r="C11">
-        <v>42300</v>
+        <v>92.342444734898</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Arauco</t>
+          <t>Santa Juana</t>
         </is>
       </c>
       <c r="C12">
-        <v>33157</v>
+        <v>92.25836617460423</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cañete</t>
+          <t>Quilaco</t>
         </is>
       </c>
       <c r="C13">
-        <v>32499</v>
+        <v>92.23439733206288</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
+          <t>Alto Biobío</t>
         </is>
       </c>
       <c r="C14">
-        <v>31472</v>
+        <v>91.94208832992103</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cabrero</t>
+          <t>Hualqui</t>
         </is>
       </c>
       <c r="C15">
-        <v>28130</v>
+        <v>91.72896069447793</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mulchén</t>
+          <t>Tucapel</t>
         </is>
       </c>
       <c r="C16">
-        <v>27693</v>
+        <v>91.64134721055014</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nacimiento</t>
+          <t>Cabrero</t>
         </is>
       </c>
       <c r="C17">
-        <v>23860</v>
+        <v>91.52729875707685</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lebu</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C18">
-        <v>23742</v>
+        <v>90.98761123713139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hualqui</t>
+          <t>Lebu</t>
         </is>
       </c>
       <c r="C19">
-        <v>22824</v>
+        <v>90.81589718088972</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Los Alamos</t>
+          <t>San Rosendo</t>
         </is>
       </c>
       <c r="C20">
-        <v>21083</v>
+        <v>90.79837618403248</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Laja</t>
+          <t>Antuco</t>
         </is>
       </c>
       <c r="C21">
-        <v>20906</v>
+        <v>90.02482509591515</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Yumbel</t>
+          <t>Coronel</t>
         </is>
       </c>
       <c r="C22">
-        <v>20008</v>
+        <v>89.55129821023444</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tucapel</t>
+          <t>Nacimiento</t>
         </is>
       </c>
       <c r="C23">
-        <v>14176</v>
+        <v>89.45375473325085</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Santa Juana</t>
+          <t>Yumbel</t>
         </is>
       </c>
       <c r="C24">
-        <v>13812</v>
+        <v>89.19003254134535</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Penco</t>
         </is>
       </c>
       <c r="C25">
-        <v>13488</v>
+        <v>88.99923129661563</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Arauco</t>
         </is>
       </c>
       <c r="C26">
-        <v>10429</v>
+        <v>88.85464680030015</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Negrete</t>
+          <t>Laja</t>
         </is>
       </c>
       <c r="C27">
-        <v>10218</v>
+        <v>88.27428957480049</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tirúa</t>
+          <t>Tomé</t>
         </is>
       </c>
       <c r="C28">
-        <v>9983</v>
+        <v>88.06259472033271</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Quilleco</t>
+          <t>Hualpén</t>
         </is>
       </c>
       <c r="C29">
-        <v>8920</v>
+        <v>84.92307342163959</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Alto Biobío</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C30">
-        <v>6287</v>
+        <v>84.88637785677538</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Contulmo</t>
+          <t>Talcahuano</t>
         </is>
       </c>
       <c r="C31">
-        <v>5749</v>
+        <v>79.90745460443132</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Antuco</t>
+          <t>Chiguayante</t>
         </is>
       </c>
       <c r="C32">
-        <v>3989</v>
+        <v>78.86050483074835</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Quilaco</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="C33">
-        <v>3872</v>
+        <v>73.61727245896429</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>San Rosendo</t>
+          <t>San Pedro de la Paz</t>
         </is>
       </c>
       <c r="C34">
-        <v>3355</v>
+        <v>72.31249577819975</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +920,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
